--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T13:03:45+00:00</t>
+    <t>2026-01-12T10:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:11:28+00:00</t>
+    <t>2026-01-12T10:18:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:18:34+00:00</t>
+    <t>2026-01-12T10:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:26:55+00:00</t>
+    <t>2026-01-28T07:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:37:37+00:00</t>
+    <t>2026-01-28T07:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:43:18+00:00</t>
+    <t>2026-01-28T07:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:44:30+00:00</t>
+    <t>2026-01-28T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:46:49+00:00</t>
+    <t>2026-02-24T18:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T18:21:42+00:00</t>
+    <t>2026-02-26T08:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:55:53+00:00</t>
+    <t>2026-03-06T07:38:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T07:38:40+00:00</t>
+    <t>2026-03-06T14:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:26:35+00:00</t>
+    <t>2026-03-09T09:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T09:58:26+00:00</t>
+    <t>2026-03-11T09:54:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T09:54:15+00:00</t>
+    <t>2026-03-18T07:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T07:58:35+00:00</t>
+    <t>2026-04-07T11:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:55:37+00:00</t>
+    <t>2026-04-08T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:58:25+00:00</t>
+    <t>2026-06-09T13:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:05:25+00:00</t>
+    <t>2026-06-09T13:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:21+00:00</t>
+    <t>2026-06-09T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T19:55:01+00:00</t>
+    <t>2026-06-10T09:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/virtual-service-detail</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/virtual-service-detail</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:07:46+00:00</t>
+    <t>2026-08-18T08:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:43:24+00:00</t>
+    <t>2026-08-18T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:20:27+00:00</t>
+    <t>2026-08-31T14:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-virtual-service-detail.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:45:12+00:00</t>
+    <t>2026-09-01T07:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
